--- a/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_Fuzzy RICE_один эксперт.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\20260218_обновленные файлы\RICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\2026.04.08_Обновление\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E806FAD-75C7-405E-909F-E94F709C5A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7481D0B2-9937-447A-B0DD-5EBA31DE01F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -408,7 +408,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -424,13 +432,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -718,103 +721,103 @@
   <sheetData>
     <row r="1" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="37" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="37" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="37" t="s">
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="39"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="33"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="32" t="s">
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="35" t="s">
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="32" t="s">
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="35" t="s">
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="32" t="s">
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="35" t="s">
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
-      <c r="AG3" s="36"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="38"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
@@ -915,7 +918,7 @@
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="6">
@@ -1016,7 +1019,7 @@
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="40" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6">
@@ -1117,7 +1120,7 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="40" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="6">
@@ -1218,7 +1221,7 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="40" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="6">
@@ -1319,7 +1322,7 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="6">
@@ -1420,7 +1423,7 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="40" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="6">
@@ -1521,7 +1524,7 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="40" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="6">
@@ -1622,7 +1625,7 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="40" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="6">
@@ -1723,7 +1726,7 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="40" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="11">
@@ -1825,11 +1828,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AG3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="N3:Q3"/>
@@ -1838,6 +1836,11 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AG3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_Fuzzy RICE_один эксперт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\2026.04.08_Обновление\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7481D0B2-9937-447A-B0DD-5EBA31DE01F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C008FC-CFA0-48C2-9325-8EE595D1037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -408,15 +408,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -432,8 +427,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -721,103 +721,103 @@
   <sheetData>
     <row r="1" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="31" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="31" t="s">
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="31" t="s">
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="33"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="40"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="34" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="34" t="s">
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="37" t="s">
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="34" t="s">
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="37" t="s">
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="34" t="s">
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="37" t="s">
+      <c r="AA3" s="34"/>
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="38"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="37"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
@@ -918,7 +918,7 @@
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="6">
@@ -952,10 +952,10 @@
         <v>2.97</v>
       </c>
       <c r="L5" s="22">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="M5" s="23">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N5" s="24">
         <v>2.94</v>
@@ -964,10 +964,10 @@
         <v>2.97</v>
       </c>
       <c r="P5" s="22">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="25">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R5" s="21">
         <v>0.873</v>
@@ -1019,7 +1019,7 @@
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6">
@@ -1120,7 +1120,7 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="6">
@@ -1221,7 +1221,7 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="6">
@@ -1255,10 +1255,10 @@
         <v>2.97</v>
       </c>
       <c r="L8" s="22">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="M8" s="23">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N8" s="24">
         <v>2.94</v>
@@ -1267,10 +1267,10 @@
         <v>2.97</v>
       </c>
       <c r="P8" s="22">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="25">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R8" s="21">
         <v>0.48499999999999999</v>
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="31" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="6">
@@ -1380,10 +1380,10 @@
         <v>0.99</v>
       </c>
       <c r="T9" s="22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="U9" s="23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="V9" s="24">
         <v>0.98</v>
@@ -1392,10 +1392,10 @@
         <v>0.99</v>
       </c>
       <c r="X9" s="22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="25">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="21">
         <v>12.61</v>
@@ -1423,7 +1423,7 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="31" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="6">
@@ -1524,7 +1524,7 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="6">
@@ -1625,7 +1625,7 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="31" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="6">
@@ -1726,7 +1726,7 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="31" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="11">
@@ -1828,6 +1828,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AG3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="N3:Q3"/>
@@ -1836,11 +1841,6 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AG3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
